--- a/LoanOfficer-A/2023/35 Salam Sunanda sat april.xlsx
+++ b/LoanOfficer-A/2023/35 Salam Sunanda sat april.xlsx
@@ -813,7 +813,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -822,7 +822,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>1400</v>
+        <v>4200</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -855,7 +855,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>65800</v>
+        <v>63000</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -895,9 +895,15 @@
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="1"/>
+      <c r="B4" s="3">
+        <v>45424</v>
+      </c>
+      <c r="C4" s="4">
+        <v>1400</v>
+      </c>
+      <c r="D4" s="1">
+        <v>1</v>
+      </c>
       <c r="E4" s="1">
         <v>32</v>
       </c>
@@ -921,9 +927,15 @@
       <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="1"/>
+      <c r="B5" s="3">
+        <v>45431</v>
+      </c>
+      <c r="C5" s="4">
+        <v>1400</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
       <c r="E5" s="1">
         <v>33</v>
       </c>

--- a/LoanOfficer-A/2023/35 Salam Sunanda sat april.xlsx
+++ b/LoanOfficer-A/2023/35 Salam Sunanda sat april.xlsx
@@ -606,7 +606,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -813,7 +813,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -822,7 +822,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>4200</v>
+        <v>7000</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -855,7 +855,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>63000</v>
+        <v>60200</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -959,9 +959,15 @@
       <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="1"/>
+      <c r="B6" s="3">
+        <v>45437</v>
+      </c>
+      <c r="C6" s="4">
+        <v>1400</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
       <c r="E6" s="1">
         <v>34</v>
       </c>
@@ -985,9 +991,15 @@
       <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="1"/>
+      <c r="B7" s="3">
+        <v>45444</v>
+      </c>
+      <c r="C7" s="4">
+        <v>1400</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
       <c r="E7" s="1">
         <v>35</v>
       </c>

--- a/LoanOfficer-A/2023/35 Salam Sunanda sat april.xlsx
+++ b/LoanOfficer-A/2023/35 Salam Sunanda sat april.xlsx
@@ -813,7 +813,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -822,7 +822,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>7000</v>
+        <v>12600</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -855,7 +855,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>60200</v>
+        <v>54600</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1023,9 +1023,15 @@
       <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="1"/>
+      <c r="B8" s="3">
+        <v>45453</v>
+      </c>
+      <c r="C8" s="4">
+        <v>1400</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
       <c r="E8" s="1">
         <v>36</v>
       </c>
@@ -1049,9 +1055,15 @@
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="1"/>
+      <c r="B9" s="3">
+        <v>45459</v>
+      </c>
+      <c r="C9" s="4">
+        <v>1400</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
       <c r="E9" s="1">
         <v>37</v>
       </c>
@@ -1075,9 +1087,15 @@
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="1"/>
+      <c r="B10" s="3">
+        <v>45466</v>
+      </c>
+      <c r="C10" s="4">
+        <v>1400</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
       <c r="E10" s="1">
         <v>38</v>
       </c>
@@ -1101,9 +1119,15 @@
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="1"/>
+      <c r="B11" s="3">
+        <v>45474</v>
+      </c>
+      <c r="C11" s="4">
+        <v>1400</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
       <c r="E11" s="1">
         <v>39</v>
       </c>

--- a/LoanOfficer-A/2023/35 Salam Sunanda sat april.xlsx
+++ b/LoanOfficer-A/2023/35 Salam Sunanda sat april.xlsx
@@ -813,7 +813,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -822,7 +822,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>12600</v>
+        <v>18200</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -855,7 +855,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>54600</v>
+        <v>49000</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1151,9 +1151,15 @@
       <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="1"/>
+      <c r="B12" s="3">
+        <v>45487</v>
+      </c>
+      <c r="C12" s="4">
+        <v>1400</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
       <c r="E12" s="1">
         <v>40</v>
       </c>
@@ -1177,9 +1183,15 @@
       <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="1"/>
+      <c r="B13" s="3">
+        <v>45500</v>
+      </c>
+      <c r="C13" s="4">
+        <v>1400</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
       <c r="E13" s="1">
         <v>41</v>
       </c>
@@ -1203,9 +1215,15 @@
       <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="1"/>
+      <c r="B14" s="3">
+        <v>45500</v>
+      </c>
+      <c r="C14" s="4">
+        <v>1400</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
       <c r="E14" s="1">
         <v>42</v>
       </c>
@@ -1229,9 +1247,15 @@
       <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="1"/>
+      <c r="B15" s="3">
+        <v>45500</v>
+      </c>
+      <c r="C15" s="4">
+        <v>1400</v>
+      </c>
+      <c r="D15" s="1">
+        <v>1</v>
+      </c>
       <c r="E15" s="1">
         <v>43</v>
       </c>

--- a/LoanOfficer-A/2023/35 Salam Sunanda sat april.xlsx
+++ b/LoanOfficer-A/2023/35 Salam Sunanda sat april.xlsx
@@ -769,7 +769,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P32"/>
+  <dimension ref="A1:P47"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="2" customWidth="1"/>
@@ -813,7 +813,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -822,7 +822,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>18200</v>
+        <v>21000</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -855,7 +855,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>49000</v>
+        <v>46200</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1279,9 +1279,15 @@
       <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="1"/>
+      <c r="B16" s="3">
+        <v>45507</v>
+      </c>
+      <c r="C16" s="4">
+        <v>1400</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
       <c r="E16" s="1">
         <v>44</v>
       </c>
@@ -1305,9 +1311,15 @@
       <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="1"/>
+      <c r="B17" s="3">
+        <v>45528</v>
+      </c>
+      <c r="C17" s="4">
+        <v>1400</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
       <c r="E17" s="1">
         <v>45</v>
       </c>
@@ -1716,6 +1728,55 @@
       <c r="N32" s="1"/>
       <c r="O32" s="4"/>
       <c r="P32" s="1"/>
+    </row>
+    <row r="39" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G39" s="2">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="40" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G40" s="2">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="41" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G41" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G42" s="2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="43" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G43" s="2">
+        <f>49+16</f>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="44" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G44" s="2">
+        <f>65*1400</f>
+        <v>91000</v>
+      </c>
+    </row>
+    <row r="45" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G45" s="2">
+        <f>91000-60000</f>
+        <v>31000</v>
+      </c>
+    </row>
+    <row r="46" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G46" s="2">
+        <f>65/4</f>
+        <v>16.25</v>
+      </c>
+    </row>
+    <row r="47" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G47" s="2">
+        <v>16.25</v>
+      </c>
     </row>
   </sheetData>
   <printOptions horizontalCentered="1"/>
